--- a/Electrical/driver_board/driver_board_v2/Pin_Layout_STM32_Robot_PCB.xlsx
+++ b/Electrical/driver_board/driver_board_v2/Pin_Layout_STM32_Robot_PCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Open-robot-arm\Electrical\driver_board\driver_board_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4AF46F7-0F1E-407F-B2F6-E6847B6CD986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A56E7E-A9E5-4ACA-BF8F-E562D42D18E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="93">
   <si>
     <t>Pin:</t>
   </si>
@@ -131,9 +131,6 @@
   </si>
   <si>
     <t>AN_GND</t>
-  </si>
-  <si>
-    <t>RENC = Rotary Encoder</t>
   </si>
   <si>
     <t>VSS</t>
@@ -308,7 +305,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -352,6 +349,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -388,18 +392,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -692,7 +697,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="2" t="s">
@@ -735,7 +740,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>19</v>
@@ -772,46 +777,46 @@
         <v>36</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>46</v>
@@ -819,27 +824,27 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="F15" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>57</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>49</v>
@@ -847,86 +852,83 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>64</v>
       </c>
       <c r="Q19" s="7"/>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>69</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -937,98 +939,128 @@
         <v>19</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C25" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="7" t="s">
-        <v>76</v>
+        <v>75</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>48</v>
+        <v>47</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>51</v>
+        <v>50</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>90</v>
+        <v>89</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C32" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>78</v>
+        <v>77</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>91</v>
+        <v>90</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>53</v>
+        <v>52</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>19</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/Electrical/driver_board/driver_board_v2/Pin_Layout_STM32_Robot_PCB.xlsx
+++ b/Electrical/driver_board/driver_board_v2/Pin_Layout_STM32_Robot_PCB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emanu\Desktop\Open-robot-arm\Electrical\driver_board\driver_board_v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85A56E7E-A9E5-4ACA-BF8F-E562D42D18E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFAD272F-66C9-4DA8-9419-CF3B027A1A9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -97,9 +97,6 @@
     <t>SW = Serial Wire</t>
   </si>
   <si>
-    <t>PA13</t>
-  </si>
-  <si>
     <t>SWDIO</t>
   </si>
   <si>
@@ -179,6 +176,9 @@
   </si>
   <si>
     <t>PB8</t>
+  </si>
+  <si>
+    <t>PB15</t>
   </si>
   <si>
     <t>PA7</t>
@@ -726,16 +726,16 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>19</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -746,80 +746,80 @@
         <v>19</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="F10" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>38</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>41</v>
-      </c>
       <c r="F13" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="F14" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -833,7 +833,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -847,7 +847,7 @@
         <v>57</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.25">
@@ -861,7 +861,7 @@
         <v>59</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.25">
@@ -933,7 +933,7 @@
     </row>
     <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
-        <v>25</v>
+        <v>52</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>19</v>
@@ -988,7 +988,7 @@
     </row>
     <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>19</v>
@@ -1010,7 +1010,7 @@
     </row>
     <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>19</v>
@@ -1054,7 +1054,7 @@
     </row>
     <row r="35" spans="1:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>19</v>
